--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/124.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/124.xlsx
@@ -426,13 +426,13 @@
         <v>-28.76964287468673</v>
       </c>
       <c r="E2">
-        <v>-7.12551517151084</v>
+        <v>-6.950598334490565</v>
       </c>
       <c r="F2">
-        <v>-0.07848831834555067</v>
+        <v>-0.327155486364191</v>
       </c>
       <c r="G2">
-        <v>-12.60666450167027</v>
+        <v>-12.29005716847653</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-28.2120035877165</v>
       </c>
       <c r="E3">
-        <v>-8.319818678501759</v>
+        <v>-7.243970994603481</v>
       </c>
       <c r="F3">
-        <v>0.09558788476180707</v>
+        <v>-0.6669411742276399</v>
       </c>
       <c r="G3">
-        <v>-11.98964833460645</v>
+        <v>-11.19490221972131</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-27.3350887511212</v>
       </c>
       <c r="E4">
-        <v>-8.801222636361164</v>
+        <v>-7.81033365332079</v>
       </c>
       <c r="F4">
-        <v>0.02609645289823956</v>
+        <v>-0.5367938058027415</v>
       </c>
       <c r="G4">
-        <v>-11.82945103596111</v>
+        <v>-10.46680069708724</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-26.20210876565354</v>
       </c>
       <c r="E5">
-        <v>-9.126339899267849</v>
+        <v>-8.669602539328226</v>
       </c>
       <c r="F5">
-        <v>-0.1010854261999984</v>
+        <v>0.06226037747729934</v>
       </c>
       <c r="G5">
-        <v>-11.06312595453062</v>
+        <v>-10.28534638553425</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-24.8453791715021</v>
       </c>
       <c r="E6">
-        <v>-10.47642291212263</v>
+        <v>-11.37977196412073</v>
       </c>
       <c r="F6">
-        <v>0.2208954479091225</v>
+        <v>-0.4943560302396683</v>
       </c>
       <c r="G6">
-        <v>-11.45389281834957</v>
+        <v>-9.483363418100263</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-23.32272862304394</v>
       </c>
       <c r="E7">
-        <v>-10.5691524743777</v>
+        <v>-10.43796258237548</v>
       </c>
       <c r="F7">
-        <v>0.3989713003059225</v>
+        <v>-0.1043098514438331</v>
       </c>
       <c r="G7">
-        <v>-10.16631241012421</v>
+        <v>-10.06748269414035</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.71330993533045</v>
       </c>
       <c r="E8">
-        <v>-11.95329414024416</v>
+        <v>-11.10196819764618</v>
       </c>
       <c r="F8">
-        <v>0.305391701468521</v>
+        <v>-0.6951010491100686</v>
       </c>
       <c r="G8">
-        <v>-9.753513865741409</v>
+        <v>-9.332144318957432</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.11258125840984</v>
       </c>
       <c r="E9">
-        <v>-12.30563658888496</v>
+        <v>-12.18086807302563</v>
       </c>
       <c r="F9">
-        <v>0.1461310672000993</v>
+        <v>0.1837773405160104</v>
       </c>
       <c r="G9">
-        <v>-9.274732838215392</v>
+        <v>-8.573691714819326</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.59090848892261</v>
       </c>
       <c r="E10">
-        <v>-13.11331257052301</v>
+        <v>-13.47641014493203</v>
       </c>
       <c r="F10">
-        <v>0.2051866689338786</v>
+        <v>0.1882457667564228</v>
       </c>
       <c r="G10">
-        <v>-8.568517332141445</v>
+        <v>-7.171245308017872</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.2279833205459</v>
       </c>
       <c r="E11">
-        <v>-13.37656635001091</v>
+        <v>-13.39794527580112</v>
       </c>
       <c r="F11">
-        <v>0.5514085376376734</v>
+        <v>0.02781319011057592</v>
       </c>
       <c r="G11">
-        <v>-7.483853502200172</v>
+        <v>-6.91247651594074</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.0726800189284</v>
       </c>
       <c r="E12">
-        <v>-14.03717560977585</v>
+        <v>-15.02334592290024</v>
       </c>
       <c r="F12">
-        <v>0.1942820618531203</v>
+        <v>0.1156866965346491</v>
       </c>
       <c r="G12">
-        <v>-6.655945652648155</v>
+        <v>-6.690650101536335</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.12489060225137</v>
       </c>
       <c r="E13">
-        <v>-14.59750181264094</v>
+        <v>-14.50035245975439</v>
       </c>
       <c r="F13">
-        <v>0.5248743368774432</v>
+        <v>0.3957128253849059</v>
       </c>
       <c r="G13">
-        <v>-5.502760151135048</v>
+        <v>-5.613779295794507</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.37618782897455</v>
       </c>
       <c r="E14">
-        <v>-16.01303486032858</v>
+        <v>-14.9710194057416</v>
       </c>
       <c r="F14">
-        <v>0.7382367407761495</v>
+        <v>0.5711478481677107</v>
       </c>
       <c r="G14">
-        <v>-5.678778546912557</v>
+        <v>-5.23906195674994</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.79489764460753</v>
       </c>
       <c r="E15">
-        <v>-16.25029519901245</v>
+        <v>-16.80472985719355</v>
       </c>
       <c r="F15">
-        <v>0.5831206648884328</v>
+        <v>0.6665376228664595</v>
       </c>
       <c r="G15">
-        <v>-4.221443295069988</v>
+        <v>-4.766584207930696</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.32705981325316</v>
       </c>
       <c r="E16">
-        <v>-17.41893131532789</v>
+        <v>-18.94766715625927</v>
       </c>
       <c r="F16">
-        <v>1.054049872197591</v>
+        <v>1.113712825149942</v>
       </c>
       <c r="G16">
-        <v>-3.578313544792392</v>
+        <v>-3.232275461754532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.93856434552317</v>
       </c>
       <c r="E17">
-        <v>-18.67176987734196</v>
+        <v>-18.55067848237685</v>
       </c>
       <c r="F17">
-        <v>1.115025717353841</v>
+        <v>0.8360464181136898</v>
       </c>
       <c r="G17">
-        <v>-3.194171082597521</v>
+        <v>-2.942238567058983</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.60323150548318</v>
       </c>
       <c r="E18">
-        <v>-19.40875185124626</v>
+        <v>-19.46588307932703</v>
       </c>
       <c r="F18">
-        <v>1.384545541161073</v>
+        <v>1.50393162789056</v>
       </c>
       <c r="G18">
-        <v>-2.10423024306665</v>
+        <v>-2.878169579237468</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.29472486453152</v>
       </c>
       <c r="E19">
-        <v>-21.27671568009223</v>
+        <v>-20.2827790340447</v>
       </c>
       <c r="F19">
-        <v>1.337723275771105</v>
+        <v>1.825916461264469</v>
       </c>
       <c r="G19">
-        <v>-1.653731206082627</v>
+        <v>-2.677742531198912</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.00619177420431</v>
       </c>
       <c r="E20">
-        <v>-21.84832231171042</v>
+        <v>-20.75529812590105</v>
       </c>
       <c r="F20">
-        <v>1.804918104531658</v>
+        <v>2.057995893524797</v>
       </c>
       <c r="G20">
-        <v>-1.746870094284483</v>
+        <v>-2.226323162554972</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.73563301721363</v>
       </c>
       <c r="E21">
-        <v>-21.80776982697174</v>
+        <v>-21.83704641143132</v>
       </c>
       <c r="F21">
-        <v>1.729988226554471</v>
+        <v>1.790720180999743</v>
       </c>
       <c r="G21">
-        <v>-1.637108956929946</v>
+        <v>-1.358682145440622</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.47823085197021</v>
       </c>
       <c r="E22">
-        <v>-22.33589857964228</v>
+        <v>-22.59446086005824</v>
       </c>
       <c r="F22">
-        <v>1.776170674754601</v>
+        <v>1.874908403758589</v>
       </c>
       <c r="G22">
-        <v>-1.278348447384667</v>
+        <v>-0.5688819855911554</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.23966088156342</v>
       </c>
       <c r="E23">
-        <v>-22.99600517879238</v>
+        <v>-24.03655793627487</v>
       </c>
       <c r="F23">
-        <v>1.894159932866671</v>
+        <v>1.77171571001447</v>
       </c>
       <c r="G23">
-        <v>-1.336974898339621</v>
+        <v>-1.461524242618081</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.03113289757582</v>
       </c>
       <c r="E24">
-        <v>-23.56807371475935</v>
+        <v>-24.62809438200082</v>
       </c>
       <c r="F24">
-        <v>1.852959823476513</v>
+        <v>2.397569364795577</v>
       </c>
       <c r="G24">
-        <v>-0.668198351769291</v>
+        <v>-1.214994537399634</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.85990010634013</v>
       </c>
       <c r="E25">
-        <v>-24.22753274212634</v>
+        <v>-24.56383080735797</v>
       </c>
       <c r="F25">
-        <v>1.842523201493767</v>
+        <v>1.593906712064421</v>
       </c>
       <c r="G25">
-        <v>-0.6827581310510057</v>
+        <v>-1.714612138549824</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.73205529216377</v>
       </c>
       <c r="E26">
-        <v>-23.06100689469848</v>
+        <v>-24.24918790483103</v>
       </c>
       <c r="F26">
-        <v>1.485745932863569</v>
+        <v>1.580118968364606</v>
       </c>
       <c r="G26">
-        <v>0.0105098314188521</v>
+        <v>-0.7185418177849879</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.652601616337</v>
       </c>
       <c r="E27">
-        <v>-24.31082496454943</v>
+        <v>-23.11765810453443</v>
       </c>
       <c r="F27">
-        <v>1.546826302610237</v>
+        <v>1.460332204038512</v>
       </c>
       <c r="G27">
-        <v>-0.4918820068932469</v>
+        <v>-0.3084314363800733</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.62135591478978</v>
       </c>
       <c r="E28">
-        <v>-24.18573945550956</v>
+        <v>-24.93750236857489</v>
       </c>
       <c r="F28">
-        <v>1.538698723852202</v>
+        <v>1.610084267990635</v>
       </c>
       <c r="G28">
-        <v>-1.50209497820185</v>
+        <v>-0.8777691265873142</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.63548101525871</v>
       </c>
       <c r="E29">
-        <v>-24.43680711144281</v>
+        <v>-24.99246445760599</v>
       </c>
       <c r="F29">
-        <v>1.376455971345008</v>
+        <v>1.161520155619312</v>
       </c>
       <c r="G29">
-        <v>-1.552885367865348</v>
+        <v>-0.2896474009902486</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.6919625695334</v>
       </c>
       <c r="E30">
-        <v>-23.93159696572508</v>
+        <v>-24.20403449050054</v>
       </c>
       <c r="F30">
-        <v>1.406929640569894</v>
+        <v>1.905830261757544</v>
       </c>
       <c r="G30">
-        <v>-1.142530006090527</v>
+        <v>-0.9751322708972798</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.78376429108769</v>
       </c>
       <c r="E31">
-        <v>-23.35008203297811</v>
+        <v>-23.54931224694557</v>
       </c>
       <c r="F31">
-        <v>1.336480066627485</v>
+        <v>1.689879290540052</v>
       </c>
       <c r="G31">
-        <v>-0.9065543200512772</v>
+        <v>-1.431113571294336</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.8974438126566</v>
       </c>
       <c r="E32">
-        <v>-22.78254649949282</v>
+        <v>-23.34137377746136</v>
       </c>
       <c r="F32">
-        <v>1.050266398765607</v>
+        <v>1.373584712520316</v>
       </c>
       <c r="G32">
-        <v>-1.268125482759398</v>
+        <v>-0.1130033121058166</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.0196807627598</v>
       </c>
       <c r="E33">
-        <v>-22.83076569072649</v>
+        <v>-23.14663580970952</v>
       </c>
       <c r="F33">
-        <v>1.242803861729242</v>
+        <v>1.676327519021636</v>
       </c>
       <c r="G33">
-        <v>-1.792317263447597</v>
+        <v>-0.7059286392803648</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.13680950731338</v>
       </c>
       <c r="E34">
-        <v>-22.35998100441507</v>
+        <v>-23.79222864966502</v>
       </c>
       <c r="F34">
-        <v>1.689953724718077</v>
+        <v>1.707537611497202</v>
       </c>
       <c r="G34">
-        <v>-1.913162107267614</v>
+        <v>-0.326470599023562</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.23249991027023</v>
       </c>
       <c r="E35">
-        <v>-21.31853160907906</v>
+        <v>-22.08632984860556</v>
       </c>
       <c r="F35">
-        <v>1.52737522655681</v>
+        <v>1.307685125672965</v>
       </c>
       <c r="G35">
-        <v>-1.245762747641621</v>
+        <v>-1.915135192409019</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.29550946389587</v>
       </c>
       <c r="E36">
-        <v>-21.92809590982954</v>
+        <v>-22.29336715176224</v>
       </c>
       <c r="F36">
-        <v>1.949724254909864</v>
+        <v>1.535779953850047</v>
       </c>
       <c r="G36">
-        <v>-1.733793439404361</v>
+        <v>0.004425048717671663</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.32158977240095</v>
       </c>
       <c r="E37">
-        <v>-20.71868994202304</v>
+        <v>-22.04525658935599</v>
       </c>
       <c r="F37">
-        <v>1.679241537906045</v>
+        <v>1.305553457510784</v>
       </c>
       <c r="G37">
-        <v>-1.46911532353963</v>
+        <v>-0.7673822961258558</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.30755547924724</v>
       </c>
       <c r="E38">
-        <v>-20.09500133084263</v>
+        <v>-21.38818859626505</v>
       </c>
       <c r="F38">
-        <v>1.981054709035002</v>
+        <v>1.864286488183736</v>
       </c>
       <c r="G38">
-        <v>-2.327298112048282</v>
+        <v>-1.223363596522912</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.25676946385503</v>
       </c>
       <c r="E39">
-        <v>-20.58831517534221</v>
+        <v>-19.88003466969852</v>
       </c>
       <c r="F39">
-        <v>2.24081098587355</v>
+        <v>2.102189207095135</v>
       </c>
       <c r="G39">
-        <v>-2.248480643849314</v>
+        <v>-0.8905180374590476</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.176341348067</v>
       </c>
       <c r="E40">
-        <v>-19.35651137509378</v>
+        <v>-20.87483172580752</v>
       </c>
       <c r="F40">
-        <v>2.133595679104214</v>
+        <v>1.8581179536431</v>
       </c>
       <c r="G40">
-        <v>-2.138325551575604</v>
+        <v>-0.8017192744591766</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.06854094290599</v>
       </c>
       <c r="E41">
-        <v>-19.56648765788144</v>
+        <v>-19.56399246870321</v>
       </c>
       <c r="F41">
-        <v>2.180522469084601</v>
+        <v>1.680860085351624</v>
       </c>
       <c r="G41">
-        <v>-2.419049881669183</v>
+        <v>-1.082344288186577</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.94001377424388</v>
       </c>
       <c r="E42">
-        <v>-18.58469185064846</v>
+        <v>-18.38161243377449</v>
       </c>
       <c r="F42">
-        <v>2.271888047052218</v>
+        <v>1.843875686345553</v>
       </c>
       <c r="G42">
-        <v>-2.387553351408557</v>
+        <v>-1.097235122022219</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.80457444974504</v>
       </c>
       <c r="E43">
-        <v>-17.62040765240316</v>
+        <v>-17.73181264146585</v>
       </c>
       <c r="F43">
-        <v>2.184766800937978</v>
+        <v>1.722772862403729</v>
       </c>
       <c r="G43">
-        <v>-3.409469101198483</v>
+        <v>-1.067854030361187</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.6697987115078</v>
       </c>
       <c r="E44">
-        <v>-16.55357163178014</v>
+        <v>-17.13801195873607</v>
       </c>
       <c r="F44">
-        <v>2.449310620758899</v>
+        <v>1.848403501557794</v>
       </c>
       <c r="G44">
-        <v>-2.512605898608987</v>
+        <v>-0.6163287242599901</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.5450877555273</v>
       </c>
       <c r="E45">
-        <v>-17.3080606861981</v>
+        <v>-17.30559266786392</v>
       </c>
       <c r="F45">
-        <v>2.313479331803489</v>
+        <v>2.037254097150286</v>
       </c>
       <c r="G45">
-        <v>-1.83532125000273</v>
+        <v>-1.681251771150589</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.44301330793006</v>
       </c>
       <c r="E46">
-        <v>-15.81317518847405</v>
+        <v>-15.64661791447194</v>
       </c>
       <c r="F46">
-        <v>2.203650910273678</v>
+        <v>1.837179777735075</v>
       </c>
       <c r="G46">
-        <v>-2.585371689562167</v>
+        <v>-1.63036868621199</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.36662794426874</v>
       </c>
       <c r="E47">
-        <v>-15.65228756392954</v>
+        <v>-16.15803206958017</v>
       </c>
       <c r="F47">
-        <v>2.347852084992186</v>
+        <v>2.184114314100817</v>
       </c>
       <c r="G47">
-        <v>-3.580591200123411</v>
+        <v>-2.225197577071619</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.32093084756532</v>
       </c>
       <c r="E48">
-        <v>-14.8824016978855</v>
+        <v>-15.15325878523228</v>
       </c>
       <c r="F48">
-        <v>2.384676414937984</v>
+        <v>2.18363761862027</v>
       </c>
       <c r="G48">
-        <v>-3.68052994886293</v>
+        <v>-1.862884852162702</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.31472104304554</v>
       </c>
       <c r="E49">
-        <v>-14.23018370045677</v>
+        <v>-14.64523645715579</v>
       </c>
       <c r="F49">
-        <v>2.054663776278713</v>
+        <v>2.088437888631374</v>
       </c>
       <c r="G49">
-        <v>-3.119296474135825</v>
+        <v>-1.927390831995401</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.34731501262686</v>
       </c>
       <c r="E50">
-        <v>-13.63881933674311</v>
+        <v>-13.88100212667333</v>
       </c>
       <c r="F50">
-        <v>2.270735109145778</v>
+        <v>1.695962304961255</v>
       </c>
       <c r="G50">
-        <v>-3.365925495720449</v>
+        <v>-2.71404597358256</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.41946134375558</v>
       </c>
       <c r="E51">
-        <v>-12.16111034093016</v>
+        <v>-15.00792194043011</v>
       </c>
       <c r="F51">
-        <v>2.384385013049544</v>
+        <v>2.222376649017834</v>
       </c>
       <c r="G51">
-        <v>-3.400451175149509</v>
+        <v>-3.020347578512548</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.5352767370516</v>
       </c>
       <c r="E52">
-        <v>-12.50152026056075</v>
+        <v>-13.81990395536184</v>
       </c>
       <c r="F52">
-        <v>2.151738614071489</v>
+        <v>1.999725018072118</v>
       </c>
       <c r="G52">
-        <v>-3.514979498080595</v>
+        <v>-1.800106977101503</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.68842985490791</v>
       </c>
       <c r="E53">
-        <v>-12.36643588091195</v>
+        <v>-14.32414047916792</v>
       </c>
       <c r="F53">
-        <v>2.162406457117889</v>
+        <v>2.064668046546543</v>
       </c>
       <c r="G53">
-        <v>-3.580031717927274</v>
+        <v>-3.099568933267308</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.87424740565074</v>
       </c>
       <c r="E54">
-        <v>-12.24268627170434</v>
+        <v>-13.21699651140263</v>
       </c>
       <c r="F54">
-        <v>1.861939436017055</v>
+        <v>1.96185544222213</v>
       </c>
       <c r="G54">
-        <v>-3.997193561330836</v>
+        <v>-3.119253437043814</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.09077211113356</v>
       </c>
       <c r="E55">
-        <v>-12.01220958708395</v>
+        <v>-11.51222077189707</v>
       </c>
       <c r="F55">
-        <v>1.919016197209493</v>
+        <v>1.740485029362004</v>
       </c>
       <c r="G55">
-        <v>-4.649073083468726</v>
+        <v>-3.25785935768202</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.32579195965178</v>
       </c>
       <c r="E56">
-        <v>-10.57902907618842</v>
+        <v>-13.22129856170992</v>
       </c>
       <c r="F56">
-        <v>2.074072092272423</v>
+        <v>1.800890740388695</v>
       </c>
       <c r="G56">
-        <v>-4.08380074318371</v>
+        <v>-3.808545434321007</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.56952464463718</v>
       </c>
       <c r="E57">
-        <v>-11.14250256848884</v>
+        <v>-11.70066868925226</v>
       </c>
       <c r="F57">
-        <v>2.255544202004883</v>
+        <v>1.341030053722543</v>
       </c>
       <c r="G57">
-        <v>-4.381693562443949</v>
+        <v>-3.600384951902714</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.81814013710929</v>
       </c>
       <c r="E58">
-        <v>-10.17244909435776</v>
+        <v>-11.68443410993476</v>
       </c>
       <c r="F58">
-        <v>1.756670503817795</v>
+        <v>1.720821736715908</v>
       </c>
       <c r="G58">
-        <v>-4.606148550006536</v>
+        <v>-3.651738134307888</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.0603722719463</v>
       </c>
       <c r="E59">
-        <v>-10.33534283288767</v>
+        <v>-11.51386913643586</v>
       </c>
       <c r="F59">
-        <v>2.174600992666773</v>
+        <v>1.697519087876132</v>
       </c>
       <c r="G59">
-        <v>-4.770884606586209</v>
+        <v>-4.356910818536965</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.28899577177063</v>
       </c>
       <c r="E60">
-        <v>-10.19671718656486</v>
+        <v>-10.16109168154652</v>
       </c>
       <c r="F60">
-        <v>1.886455203588058</v>
+        <v>1.606473418503433</v>
       </c>
       <c r="G60">
-        <v>-5.207638258491178</v>
+        <v>-4.480377614424084</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.5021095287798</v>
       </c>
       <c r="E61">
-        <v>-10.44082004947432</v>
+        <v>-9.724030541170222</v>
       </c>
       <c r="F61">
-        <v>2.181768845640052</v>
+        <v>1.954149129237601</v>
       </c>
       <c r="G61">
-        <v>-4.933064922009565</v>
+        <v>-3.778131452451723</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.69060326034431</v>
       </c>
       <c r="E62">
-        <v>-9.662361782133766</v>
+        <v>-10.38350768243325</v>
       </c>
       <c r="F62">
-        <v>2.127569678095967</v>
+        <v>1.590026632571595</v>
       </c>
       <c r="G62">
-        <v>-5.567004597870144</v>
+        <v>-4.421631983829717</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.84965303648588</v>
       </c>
       <c r="E63">
-        <v>-8.405003803060046</v>
+        <v>-10.03675337071791</v>
       </c>
       <c r="F63">
-        <v>2.045178961551145</v>
+        <v>1.414406316196683</v>
       </c>
       <c r="G63">
-        <v>-5.424502165132216</v>
+        <v>-5.170911066278504</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.9787070733213</v>
       </c>
       <c r="E64">
-        <v>-9.294441382906582</v>
+        <v>-8.78453068116889</v>
       </c>
       <c r="F64">
-        <v>1.505013299030805</v>
+        <v>1.595113495971986</v>
       </c>
       <c r="G64">
-        <v>-5.188013344534379</v>
+        <v>-4.703541489226355</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.07032191582086</v>
       </c>
       <c r="E65">
-        <v>-9.030589844849668</v>
+        <v>-10.24923842810582</v>
       </c>
       <c r="F65">
-        <v>1.701780840494579</v>
+        <v>1.712863614490824</v>
       </c>
       <c r="G65">
-        <v>-5.902051669717624</v>
+        <v>-4.450341034746277</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.12191325722198</v>
       </c>
       <c r="E66">
-        <v>-8.724523872093251</v>
+        <v>-9.728921293098505</v>
       </c>
       <c r="F66">
-        <v>1.778520894333113</v>
+        <v>1.860274961099928</v>
       </c>
       <c r="G66">
-        <v>-6.001814959543561</v>
+        <v>-4.164674060162565</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.13491849792957</v>
       </c>
       <c r="E67">
-        <v>-8.417416350315071</v>
+        <v>-8.755906196966407</v>
       </c>
       <c r="F67">
-        <v>1.463211381392781</v>
+        <v>1.187904696170534</v>
       </c>
       <c r="G67">
-        <v>-5.691540699966448</v>
+        <v>-4.731853274678202</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.10554667843519</v>
       </c>
       <c r="E68">
-        <v>-7.970365396277853</v>
+        <v>-8.492634303582475</v>
       </c>
       <c r="F68">
-        <v>1.629391226805758</v>
+        <v>1.28361121205237</v>
       </c>
       <c r="G68">
-        <v>-5.225965438596583</v>
+        <v>-4.667396953028592</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.03512607203483</v>
       </c>
       <c r="E69">
-        <v>-8.86442654808622</v>
+        <v>-8.663846848864477</v>
       </c>
       <c r="F69">
-        <v>1.426068726557979</v>
+        <v>1.215690816456919</v>
       </c>
       <c r="G69">
-        <v>-5.988271517742403</v>
+        <v>-5.754470860122454</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.92929949535606</v>
       </c>
       <c r="E70">
-        <v>-8.637060925109106</v>
+        <v>-9.627134782828099</v>
       </c>
       <c r="F70">
-        <v>1.560094590769789</v>
+        <v>0.8237726972690341</v>
       </c>
       <c r="G70">
-        <v>-6.377091780784265</v>
+        <v>-5.206161755180664</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.78921924533215</v>
       </c>
       <c r="E71">
-        <v>-8.829792778875557</v>
+        <v>-8.977339518993473</v>
       </c>
       <c r="F71">
-        <v>1.266611712756043</v>
+        <v>1.143663871422733</v>
       </c>
       <c r="G71">
-        <v>-5.198832207356717</v>
+        <v>-5.268539054231611</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.61920155563222</v>
       </c>
       <c r="E72">
-        <v>-9.121820482208195</v>
+        <v>-9.350245768103102</v>
       </c>
       <c r="F72">
-        <v>1.125633379575455</v>
+        <v>1.1342645768146</v>
       </c>
       <c r="G72">
-        <v>-5.775165080288438</v>
+        <v>-5.385315237583863</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.42665318397254</v>
       </c>
       <c r="E73">
-        <v>-8.765121641572016</v>
+        <v>-9.579812229447944</v>
       </c>
       <c r="F73">
-        <v>1.264540225418648</v>
+        <v>1.092926685009799</v>
       </c>
       <c r="G73">
-        <v>-5.786632810036473</v>
+        <v>-5.058441902672843</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.21428483005722</v>
       </c>
       <c r="E74">
-        <v>-8.91764970309837</v>
+        <v>-8.348121641049699</v>
       </c>
       <c r="F74">
-        <v>1.173806546111292</v>
+        <v>0.7285286235145058</v>
       </c>
       <c r="G74">
-        <v>-5.509642775311193</v>
+        <v>-6.0758586210749</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.98764875322455</v>
       </c>
       <c r="E75">
-        <v>-10.0174982992373</v>
+        <v>-10.26189551295726</v>
       </c>
       <c r="F75">
-        <v>1.054178152376742</v>
+        <v>0.9299680974288262</v>
       </c>
       <c r="G75">
-        <v>-5.388486740210484</v>
+        <v>-5.502286743122932</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.75574985780673</v>
       </c>
       <c r="E76">
-        <v>-9.910802923142578</v>
+        <v>-9.548176310030358</v>
       </c>
       <c r="F76">
-        <v>0.8909281629073285</v>
+        <v>0.6654179427842438</v>
       </c>
       <c r="G76">
-        <v>-4.820248151122282</v>
+        <v>-4.634907259106185</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.52507740462636</v>
       </c>
       <c r="E77">
-        <v>-9.36605467086388</v>
+        <v>-10.89408859832407</v>
       </c>
       <c r="F77">
-        <v>0.8895170809366719</v>
+        <v>0.8621680634829481</v>
       </c>
       <c r="G77">
-        <v>-5.213133764086368</v>
+        <v>-5.400020680869305</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.30353143040102</v>
       </c>
       <c r="E78">
-        <v>-10.2862451176965</v>
+        <v>-10.16602771821488</v>
       </c>
       <c r="F78">
-        <v>0.6814244584715903</v>
+        <v>0.9094591058238854</v>
       </c>
       <c r="G78">
-        <v>-4.791039207829292</v>
+        <v>-5.397554324442549</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.1023585089059</v>
       </c>
       <c r="E79">
-        <v>-9.926186149346634</v>
+        <v>-10.54502023639082</v>
       </c>
       <c r="F79">
-        <v>0.5569214179293182</v>
+        <v>0.8169722640681372</v>
       </c>
       <c r="G79">
-        <v>-5.417165996217191</v>
+        <v>-4.328185214892709</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.92942727698229</v>
       </c>
       <c r="E80">
-        <v>-11.13394828108835</v>
+        <v>-11.27283205042959</v>
       </c>
       <c r="F80">
-        <v>0.9594852082807867</v>
+        <v>0.5871812868556197</v>
       </c>
       <c r="G80">
-        <v>-5.013421793884295</v>
+        <v>-4.048391148095665</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.78966524318462</v>
       </c>
       <c r="E81">
-        <v>-12.39147834217436</v>
+        <v>-12.28903520317284</v>
       </c>
       <c r="F81">
-        <v>0.7758640096210754</v>
+        <v>0.3466804983899429</v>
       </c>
       <c r="G81">
-        <v>-5.4247537665932</v>
+        <v>-4.946227651073707</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.68856064297662</v>
       </c>
       <c r="E82">
-        <v>-12.10341305359843</v>
+        <v>-12.23611545591921</v>
       </c>
       <c r="F82">
-        <v>0.6218628626978281</v>
+        <v>0.6397112283648306</v>
       </c>
       <c r="G82">
-        <v>-4.274822531345197</v>
+        <v>-4.469035685406541</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.62935200995871</v>
       </c>
       <c r="E83">
-        <v>-13.45935138334513</v>
+        <v>-13.21299786885386</v>
       </c>
       <c r="F83">
-        <v>0.7827420444118289</v>
+        <v>1.032212151329597</v>
       </c>
       <c r="G83">
-        <v>-4.861255878717234</v>
+        <v>-4.453562195555987</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.61153881611273</v>
       </c>
       <c r="E84">
-        <v>-14.07949419937753</v>
+        <v>-14.95549579684331</v>
       </c>
       <c r="F84">
-        <v>0.8821718529008638</v>
+        <v>0.715079792880594</v>
       </c>
       <c r="G84">
-        <v>-4.60344714484649</v>
+        <v>-4.179766837276103</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.63668057417554</v>
       </c>
       <c r="E85">
-        <v>-15.56659072180839</v>
+        <v>-14.9147531161963</v>
       </c>
       <c r="F85">
-        <v>0.8517045184996397</v>
+        <v>0.4917867610391245</v>
       </c>
       <c r="G85">
-        <v>-4.893076842440709</v>
+        <v>-4.494970499161191</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.70629594786389</v>
       </c>
       <c r="E86">
-        <v>-15.70727229533067</v>
+        <v>-15.51980252836114</v>
       </c>
       <c r="F86">
-        <v>1.0782995771748</v>
+        <v>0.8472147122293688</v>
       </c>
       <c r="G86">
-        <v>-4.062414619000018</v>
+        <v>-3.258236759873497</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.81578207261789</v>
       </c>
       <c r="E87">
-        <v>-18.33475178474312</v>
+        <v>-18.0390786598343</v>
       </c>
       <c r="F87">
-        <v>0.7739049654036768</v>
+        <v>0.7697651581407181</v>
       </c>
       <c r="G87">
-        <v>-4.137153495094604</v>
+        <v>-3.245799040282455</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.96028713510043</v>
       </c>
       <c r="E88">
-        <v>-18.96230771272607</v>
+        <v>-18.90269035241509</v>
       </c>
       <c r="F88">
-        <v>0.6634699845082532</v>
+        <v>0.2939335891703166</v>
       </c>
       <c r="G88">
-        <v>-3.835516448829449</v>
+        <v>-3.001153035475854</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.13278967348994</v>
       </c>
       <c r="E89">
-        <v>-20.8876880635153</v>
+        <v>-21.56066911426919</v>
       </c>
       <c r="F89">
-        <v>1.104082309478155</v>
+        <v>0.6291669143798349</v>
       </c>
       <c r="G89">
-        <v>-3.92817861847365</v>
+        <v>-4.254217695908773</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.31593319695787</v>
       </c>
       <c r="E90">
-        <v>-22.51192489279444</v>
+        <v>-22.41990630095858</v>
       </c>
       <c r="F90">
-        <v>0.7316263522851053</v>
+        <v>0.5744546261191482</v>
       </c>
       <c r="G90">
-        <v>-3.557705398810429</v>
+        <v>-2.759417000198272</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.4895934513229</v>
       </c>
       <c r="E91">
-        <v>-23.83309359911024</v>
+        <v>-25.20177052624052</v>
       </c>
       <c r="F91">
-        <v>0.8062648283738511</v>
+        <v>0.4881133551682627</v>
       </c>
       <c r="G91">
-        <v>-2.980025133844225</v>
+        <v>-3.451436886999824</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.63313594391555</v>
       </c>
       <c r="E92">
-        <v>-25.20324680876702</v>
+        <v>-25.67222916242338</v>
       </c>
       <c r="F92">
-        <v>0.6765133864278126</v>
+        <v>0.5109210959094639</v>
       </c>
       <c r="G92">
-        <v>-3.566273090666063</v>
+        <v>-2.461448038390629</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.71890228208999</v>
       </c>
       <c r="E93">
-        <v>-27.52802498161074</v>
+        <v>-28.31044566370801</v>
       </c>
       <c r="F93">
-        <v>0.1889425973592162</v>
+        <v>0.4330534434591372</v>
       </c>
       <c r="G93">
-        <v>-3.279950628065577</v>
+        <v>-2.582276329482949</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.72602200227976</v>
       </c>
       <c r="E94">
-        <v>-30.19947368940066</v>
+        <v>-30.88489672249063</v>
       </c>
       <c r="F94">
-        <v>0.6321537837363537</v>
+        <v>0.4392306883823087</v>
       </c>
       <c r="G94">
-        <v>-3.336766210610549</v>
+        <v>-2.965750061478888</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.64694218393271</v>
       </c>
       <c r="E95">
-        <v>-31.68628718220603</v>
+        <v>-33.7924147803004</v>
       </c>
       <c r="F95">
-        <v>0.3404145659355067</v>
+        <v>0.4432469665838632</v>
       </c>
       <c r="G95">
-        <v>-3.382296143412145</v>
+        <v>-2.824207686947348</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.48006246471039</v>
       </c>
       <c r="E96">
-        <v>-34.53743026709432</v>
+        <v>-35.34633572942544</v>
       </c>
       <c r="F96">
-        <v>0.02985537888853509</v>
+        <v>0.4695475707215661</v>
       </c>
       <c r="G96">
-        <v>-2.908560387287978</v>
+        <v>-1.885313798191264</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.23702129330094</v>
       </c>
       <c r="E97">
-        <v>-37.01598862452751</v>
+        <v>-36.99146920201298</v>
       </c>
       <c r="F97">
-        <v>0.1208812519372905</v>
+        <v>0.1905041313918395</v>
       </c>
       <c r="G97">
-        <v>-3.290272909057024</v>
+        <v>-3.177287300347238</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.94642489086594</v>
       </c>
       <c r="E98">
-        <v>-40.15242330766203</v>
+        <v>-40.97087252896431</v>
       </c>
       <c r="F98">
-        <v>0.1425796066847264</v>
+        <v>0.05423257219193679</v>
       </c>
       <c r="G98">
-        <v>-3.184570500533634</v>
+        <v>-3.16896789940705</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.63021944944114</v>
       </c>
       <c r="E99">
-        <v>-42.63690943757126</v>
+        <v>-43.68833279690917</v>
       </c>
       <c r="F99">
-        <v>-0.2530808095813417</v>
+        <v>-0.06458338040799232</v>
       </c>
       <c r="G99">
-        <v>-3.490534429818617</v>
+        <v>-3.127996587813029</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.32547150934891</v>
       </c>
       <c r="E100">
-        <v>-45.8133848878816</v>
+        <v>-45.57433353772769</v>
       </c>
       <c r="F100">
-        <v>-0.1168567615589022</v>
+        <v>-0.1634628510914119</v>
       </c>
       <c r="G100">
-        <v>-3.669396584214361</v>
+        <v>-3.698701533327989</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.05736510556177</v>
       </c>
       <c r="E101">
-        <v>-47.81444736052401</v>
+        <v>-47.97041026958518</v>
       </c>
       <c r="F101">
-        <v>-0.494142229941084</v>
+        <v>-0.07246152548434585</v>
       </c>
       <c r="G101">
-        <v>-4.126460433002759</v>
+        <v>-3.147065330119231</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.8665041639797</v>
       </c>
       <c r="E102">
-        <v>-49.65872500607286</v>
+        <v>-50.88585202478987</v>
       </c>
       <c r="F102">
-        <v>-0.6045019848055242</v>
+        <v>-0.2958757108283464</v>
       </c>
       <c r="G102">
-        <v>-3.362684471637503</v>
+        <v>-2.941003733572836</v>
       </c>
     </row>
   </sheetData>
